--- a/data/nzd0503/nzd0503.xlsx
+++ b/data/nzd0503/nzd0503.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H383"/>
+  <dimension ref="A1:H385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11900,6 +11900,66 @@
       <c r="H383" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>255.19</v>
+      </c>
+      <c r="C384" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="D384" t="n">
+        <v>326.86</v>
+      </c>
+      <c r="E384" t="n">
+        <v>329.95</v>
+      </c>
+      <c r="F384" t="n">
+        <v>327.78</v>
+      </c>
+      <c r="G384" t="n">
+        <v>405.1</v>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>283.69</v>
+      </c>
+      <c r="C385" t="n">
+        <v>285.15</v>
+      </c>
+      <c r="D385" t="n">
+        <v>327.64</v>
+      </c>
+      <c r="E385" t="n">
+        <v>330.05</v>
+      </c>
+      <c r="F385" t="n">
+        <v>329.24</v>
+      </c>
+      <c r="G385" t="n">
+        <v>404.28</v>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B443"/>
+  <dimension ref="A1:B445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16347,6 +16407,26 @@
       </c>
       <c r="B443" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -16515,28 +16595,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.052787979574056</v>
+        <v>-1.059652948957841</v>
       </c>
       <c r="J2" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K2" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02566104308720396</v>
+        <v>0.02623534587346132</v>
       </c>
       <c r="M2" t="n">
-        <v>35.67814726404552</v>
+        <v>35.56910873593369</v>
       </c>
       <c r="N2" t="n">
-        <v>1870.861060920535</v>
+        <v>1862.049352905772</v>
       </c>
       <c r="O2" t="n">
-        <v>43.25345143362014</v>
+        <v>43.1514698811729</v>
       </c>
       <c r="P2" t="n">
-        <v>303.2851485501507</v>
+        <v>303.3689645524213</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16593,28 +16673,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.033086401817155</v>
+        <v>-2.046519196008443</v>
       </c>
       <c r="J3" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K3" t="n">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1928841616037447</v>
+        <v>0.1962209946443345</v>
       </c>
       <c r="M3" t="n">
-        <v>19.75173226536445</v>
+        <v>19.73384426593978</v>
       </c>
       <c r="N3" t="n">
-        <v>787.5081086930818</v>
+        <v>785.0703459456898</v>
       </c>
       <c r="O3" t="n">
-        <v>28.06257487639154</v>
+        <v>28.01910680135414</v>
       </c>
       <c r="P3" t="n">
-        <v>338.2064502191756</v>
+        <v>338.3677058193979</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16671,28 +16751,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.049984703054836</v>
+        <v>-1.025792224468718</v>
       </c>
       <c r="J4" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K4" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3294359902133479</v>
+        <v>0.3159830245062029</v>
       </c>
       <c r="M4" t="n">
-        <v>8.097030130052397</v>
+        <v>8.187954763518926</v>
       </c>
       <c r="N4" t="n">
-        <v>101.9796350784607</v>
+        <v>104.0383355094487</v>
       </c>
       <c r="O4" t="n">
-        <v>10.09849667418179</v>
+        <v>10.19991840699957</v>
       </c>
       <c r="P4" t="n">
-        <v>332.3869575333189</v>
+        <v>332.0962827862587</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16749,28 +16829,28 @@
         <v>0.0806</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8468109436537066</v>
+        <v>-0.8232635825179998</v>
       </c>
       <c r="J5" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K5" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3199487866241605</v>
+        <v>0.3025642223863179</v>
       </c>
       <c r="M5" t="n">
-        <v>6.566382592390296</v>
+        <v>6.66461707430597</v>
       </c>
       <c r="N5" t="n">
-        <v>69.26476874047866</v>
+        <v>71.35689121185307</v>
       </c>
       <c r="O5" t="n">
-        <v>8.322545808854324</v>
+        <v>8.447300824041552</v>
       </c>
       <c r="P5" t="n">
-        <v>330.393415029691</v>
+        <v>330.1104934213149</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16827,28 +16907,28 @@
         <v>0.059</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7094994992980374</v>
+        <v>-0.6936471544984145</v>
       </c>
       <c r="J6" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K6" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2535725576416801</v>
+        <v>0.2439640974813777</v>
       </c>
       <c r="M6" t="n">
-        <v>6.431933748171992</v>
+        <v>6.482786651833668</v>
       </c>
       <c r="N6" t="n">
-        <v>67.3391834161993</v>
+        <v>68.10283332680065</v>
       </c>
       <c r="O6" t="n">
-        <v>8.206045540709564</v>
+        <v>8.252444082015984</v>
       </c>
       <c r="P6" t="n">
-        <v>332.4450708423798</v>
+        <v>332.2546006661349</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16905,28 +16985,28 @@
         <v>0.1629</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4018156014011009</v>
+        <v>-0.3815647930009005</v>
       </c>
       <c r="J7" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K7" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09841785121461732</v>
+        <v>0.08827619662149089</v>
       </c>
       <c r="M7" t="n">
-        <v>6.61859582370354</v>
+        <v>6.678533740704604</v>
       </c>
       <c r="N7" t="n">
-        <v>67.21455507327043</v>
+        <v>68.67959617396431</v>
       </c>
       <c r="O7" t="n">
-        <v>8.19844833326834</v>
+        <v>8.287315377971584</v>
       </c>
       <c r="P7" t="n">
-        <v>396.4457523834967</v>
+        <v>396.2024416386898</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16964,7 +17044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H383"/>
+  <dimension ref="A1:H385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32993,6 +33073,90 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-45.7879694021785,170.74027354559874</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-45.788593265682806,170.74007875476664</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-45.78936910662075,170.74069595546544</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-45.789983945174065,170.7405169401856</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-45.790589356650734,170.7402683735022</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>-45.791343936518224,170.74108238448403</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>-45.788043179023056,170.7406245738262</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>-45.78865688339218,170.74039785726873</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-45.78937093421899,170.74070564082982</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-45.78998418119075,170.74051818125096</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>-45.790592392952114,170.7402866423224</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>-45.79134247783858,170.74107204636047</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0503/nzd0503.xlsx
+++ b/data/nzd0503/nzd0503.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11958,6 +11958,36 @@
         <v>404.28</v>
       </c>
       <c r="H385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>331.14</v>
+      </c>
+      <c r="C386" t="n">
+        <v>334.11</v>
+      </c>
+      <c r="D386" t="n">
+        <v>332.67</v>
+      </c>
+      <c r="E386" t="n">
+        <v>330.76</v>
+      </c>
+      <c r="F386" t="n">
+        <v>330.27</v>
+      </c>
+      <c r="G386" t="n">
+        <v>400.83</v>
+      </c>
+      <c r="H386" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11974,7 +12004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16427,6 +16457,16 @@
       </c>
       <c r="B445" t="n">
         <v>0.21</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>-0.12</v>
       </c>
     </row>
   </sheetData>
@@ -16595,28 +16635,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.059652948957841</v>
+        <v>-1.028534712610454</v>
       </c>
       <c r="J2" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K2" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02623534587346132</v>
+        <v>0.0247728292421211</v>
       </c>
       <c r="M2" t="n">
-        <v>35.56910873593369</v>
+        <v>35.59232598622702</v>
       </c>
       <c r="N2" t="n">
-        <v>1862.049352905772</v>
+        <v>1865.331104345506</v>
       </c>
       <c r="O2" t="n">
-        <v>43.1514698811729</v>
+        <v>43.18947909324105</v>
       </c>
       <c r="P2" t="n">
-        <v>303.3689645524213</v>
+        <v>302.9874242535078</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16673,28 +16713,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.046519196008443</v>
+        <v>-2.019764761208411</v>
       </c>
       <c r="J3" t="n">
+        <v>385</v>
+      </c>
+      <c r="K3" t="n">
         <v>384</v>
       </c>
-      <c r="K3" t="n">
-        <v>383</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.1962209946443345</v>
+        <v>0.1916394485819199</v>
       </c>
       <c r="M3" t="n">
-        <v>19.73384426593978</v>
+        <v>19.77612625959121</v>
       </c>
       <c r="N3" t="n">
-        <v>785.0703459456898</v>
+        <v>789.4106548882816</v>
       </c>
       <c r="O3" t="n">
-        <v>28.01910680135414</v>
+        <v>28.09645271005366</v>
       </c>
       <c r="P3" t="n">
-        <v>338.3677058193979</v>
+        <v>338.0453636901919</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16751,28 +16791,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.025792224468718</v>
+        <v>-1.010921824504639</v>
       </c>
       <c r="J4" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K4" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3159830245062029</v>
+        <v>0.3067973560405923</v>
       </c>
       <c r="M4" t="n">
-        <v>8.187954763518926</v>
+        <v>8.248863297520204</v>
       </c>
       <c r="N4" t="n">
-        <v>104.0383355094487</v>
+        <v>105.7344148642873</v>
       </c>
       <c r="O4" t="n">
-        <v>10.19991840699957</v>
+        <v>10.28272409745041</v>
       </c>
       <c r="P4" t="n">
-        <v>332.0962827862587</v>
+        <v>331.9170563186296</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16829,28 +16869,28 @@
         <v>0.0806</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8232635825179998</v>
+        <v>-0.8112241210303874</v>
       </c>
       <c r="J5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3025642223863179</v>
+        <v>0.2937184146381502</v>
       </c>
       <c r="M5" t="n">
-        <v>6.66461707430597</v>
+        <v>6.714939488019816</v>
       </c>
       <c r="N5" t="n">
-        <v>71.35689121185307</v>
+        <v>72.4604525631254</v>
       </c>
       <c r="O5" t="n">
-        <v>8.447300824041552</v>
+        <v>8.51237056072663</v>
       </c>
       <c r="P5" t="n">
-        <v>330.1104934213149</v>
+        <v>329.9653870247289</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16907,28 +16947,28 @@
         <v>0.059</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6936471544984145</v>
+        <v>-0.6848705872310755</v>
       </c>
       <c r="J6" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K6" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2439640974813777</v>
+        <v>0.2384072317498798</v>
       </c>
       <c r="M6" t="n">
-        <v>6.482786651833668</v>
+        <v>6.512690235628198</v>
       </c>
       <c r="N6" t="n">
-        <v>68.10283332680065</v>
+        <v>68.61088800000668</v>
       </c>
       <c r="O6" t="n">
-        <v>8.252444082015984</v>
+        <v>8.28316895879872</v>
       </c>
       <c r="P6" t="n">
-        <v>332.2546006661349</v>
+        <v>332.1488205154307</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16985,28 +17025,28 @@
         <v>0.1629</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3815647930009005</v>
+        <v>-0.3736556336009619</v>
       </c>
       <c r="J7" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K7" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08827619662149089</v>
+        <v>0.0847330627859636</v>
       </c>
       <c r="M7" t="n">
-        <v>6.678533740704604</v>
+        <v>6.698081114462796</v>
       </c>
       <c r="N7" t="n">
-        <v>68.67959617396431</v>
+        <v>69.05745384116837</v>
       </c>
       <c r="O7" t="n">
-        <v>8.287315377971584</v>
+        <v>8.31008145815481</v>
       </c>
       <c r="P7" t="n">
-        <v>396.2024416386898</v>
+        <v>396.1071159780088</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17044,7 +17084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H385"/>
+  <dimension ref="A1:H386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33157,6 +33197,48 @@
         </is>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>-45.78816600863997,170.74120900717267</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>-45.788777606675346,170.74100341200787</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>-45.789382719864996,170.7407680990289</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>-45.78998585690895,170.7405269928152</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>-45.79059453499861,170.74029953060088</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>-45.79133634070067,170.74102855060303</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0503/nzd0503.xlsx
+++ b/data/nzd0503/nzd0503.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H386"/>
+  <dimension ref="A1:H388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11955,7 +11955,7 @@
         <v>329.24</v>
       </c>
       <c r="G385" t="n">
-        <v>404.28</v>
+        <v>398.71</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
@@ -11985,11 +11985,71 @@
         <v>330.27</v>
       </c>
       <c r="G386" t="n">
-        <v>400.83</v>
+        <v>393.98</v>
       </c>
       <c r="H386" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>340.22</v>
+      </c>
+      <c r="C387" t="n">
+        <v>339.74</v>
+      </c>
+      <c r="D387" t="n">
+        <v>337.64</v>
+      </c>
+      <c r="E387" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="F387" t="n">
+        <v>332.96</v>
+      </c>
+      <c r="G387" t="n">
+        <v>387.98</v>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>335.63</v>
+      </c>
+      <c r="C388" t="n">
+        <v>332.79</v>
+      </c>
+      <c r="D388" t="n">
+        <v>332.25</v>
+      </c>
+      <c r="E388" t="n">
+        <v>328.34</v>
+      </c>
+      <c r="F388" t="n">
+        <v>330.17</v>
+      </c>
+      <c r="G388" t="n">
+        <v>383.34</v>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12004,7 +12064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B446"/>
+  <dimension ref="A1:B449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16467,6 +16527,36 @@
       </c>
       <c r="B446" t="n">
         <v>-0.12</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>-0.72</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>-0.88</v>
       </c>
     </row>
   </sheetData>
@@ -16635,28 +16725,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.028534712610454</v>
+        <v>-0.9588932221924883</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K2" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0247728292421211</v>
+        <v>0.02159454132025529</v>
       </c>
       <c r="M2" t="n">
-        <v>35.59232598622702</v>
+        <v>35.66235165502599</v>
       </c>
       <c r="N2" t="n">
-        <v>1865.331104345506</v>
+        <v>1875.793071407199</v>
       </c>
       <c r="O2" t="n">
-        <v>43.18947909324105</v>
+        <v>43.31042682088458</v>
       </c>
       <c r="P2" t="n">
-        <v>302.9874242535078</v>
+        <v>302.1276245708785</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16713,28 +16803,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.019764761208411</v>
+        <v>-1.963892428017042</v>
       </c>
       <c r="J3" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K3" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1916394485819199</v>
+        <v>0.1820675659345196</v>
       </c>
       <c r="M3" t="n">
-        <v>19.77612625959121</v>
+        <v>19.8730961434155</v>
       </c>
       <c r="N3" t="n">
-        <v>789.4106548882816</v>
+        <v>799.076040503926</v>
       </c>
       <c r="O3" t="n">
-        <v>28.09645271005366</v>
+        <v>28.267933078029</v>
       </c>
       <c r="P3" t="n">
-        <v>338.0453636901919</v>
+        <v>337.3675454250783</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16791,28 +16881,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.010921824504639</v>
+        <v>-0.97872053301242</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K4" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3067973560405923</v>
+        <v>0.2866001942685659</v>
       </c>
       <c r="M4" t="n">
-        <v>8.248863297520204</v>
+        <v>8.381710642604098</v>
       </c>
       <c r="N4" t="n">
-        <v>105.7344148642873</v>
+        <v>109.7601156735898</v>
       </c>
       <c r="O4" t="n">
-        <v>10.28272409745041</v>
+        <v>10.47664620351331</v>
       </c>
       <c r="P4" t="n">
-        <v>331.9170563186296</v>
+        <v>331.5262775546947</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16869,28 +16959,28 @@
         <v>0.0806</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8112241210303874</v>
+        <v>-0.7872821939903559</v>
       </c>
       <c r="J5" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K5" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2937184146381502</v>
+        <v>0.2766012641192223</v>
       </c>
       <c r="M5" t="n">
-        <v>6.714939488019816</v>
+        <v>6.81255184642412</v>
       </c>
       <c r="N5" t="n">
-        <v>72.4604525631254</v>
+        <v>74.61997402340501</v>
       </c>
       <c r="O5" t="n">
-        <v>8.51237056072663</v>
+        <v>8.638285363624254</v>
       </c>
       <c r="P5" t="n">
-        <v>329.9653870247289</v>
+        <v>329.6748414862465</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16947,28 +17037,28 @@
         <v>0.059</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6848705872310755</v>
+        <v>-0.6658998373743691</v>
       </c>
       <c r="J6" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K6" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2384072317498798</v>
+        <v>0.2261674342983083</v>
       </c>
       <c r="M6" t="n">
-        <v>6.512690235628198</v>
+        <v>6.578625937854235</v>
       </c>
       <c r="N6" t="n">
-        <v>68.61088800000668</v>
+        <v>69.84018791560976</v>
       </c>
       <c r="O6" t="n">
-        <v>8.28316895879872</v>
+        <v>8.357044209265005</v>
       </c>
       <c r="P6" t="n">
-        <v>332.1488205154307</v>
+        <v>331.9185998527573</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17025,28 +17115,28 @@
         <v>0.1629</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3736556336009619</v>
+        <v>-0.3807994798925088</v>
       </c>
       <c r="J7" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K7" t="n">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0847330627859636</v>
+        <v>0.08951753131334528</v>
       </c>
       <c r="M7" t="n">
-        <v>6.698081114462796</v>
+        <v>6.644461566827009</v>
       </c>
       <c r="N7" t="n">
-        <v>69.05745384116837</v>
+        <v>67.89328689476285</v>
       </c>
       <c r="O7" t="n">
-        <v>8.31008145815481</v>
+        <v>8.239738278292755</v>
       </c>
       <c r="P7" t="n">
-        <v>396.1071159780088</v>
+        <v>396.1931749007869</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17084,7 +17174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H386"/>
+  <dimension ref="A1:H388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33188,7 +33278,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>-45.79134247783858,170.74107204636047</t>
+          <t>-45.791332569465766,170.7410018227803</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -33230,12 +33320,96 @@
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>-45.79133634070067,170.74102855060303</t>
+          <t>-45.79132415532027,170.74094218949153</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:31+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>-45.788189512896835,170.74132084424846</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>-45.78879148866372,170.74107304603052</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>-45.78939436489367,170.74082981222685</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-45.78999097846607,170.74055392393763</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>-45.79060012926863,170.74033319028456</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>-45.79131348194127,170.74086654475528</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>-45.78817763135316,170.7412643098554</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>-45.78877435192247,170.74098708574138</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>-45.78938173577655,170.7407628838303</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-45.789980145303325,170.74049695903506</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>-45.790594327033006,170.74029827931165</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>-45.7913052278275,170.74080804618035</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0503/nzd0503.xlsx
+++ b/data/nzd0503/nzd0503.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H388"/>
+  <dimension ref="A1:H394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12048,6 +12048,186 @@
         <v>383.34</v>
       </c>
       <c r="H388" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>313.88</v>
+      </c>
+      <c r="C389" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="D389" t="n">
+        <v>330.54</v>
+      </c>
+      <c r="E389" t="n">
+        <v>324.18</v>
+      </c>
+      <c r="F389" t="n">
+        <v>329.51</v>
+      </c>
+      <c r="G389" t="n">
+        <v>380.58</v>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>293.27</v>
+      </c>
+      <c r="C390" t="n">
+        <v>331.82</v>
+      </c>
+      <c r="D390" t="n">
+        <v>331.42</v>
+      </c>
+      <c r="E390" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="F390" t="n">
+        <v>329.2</v>
+      </c>
+      <c r="G390" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>277.57</v>
+      </c>
+      <c r="C391" t="n">
+        <v>326.87</v>
+      </c>
+      <c r="D391" t="n">
+        <v>328.96</v>
+      </c>
+      <c r="E391" t="n">
+        <v>322.36</v>
+      </c>
+      <c r="F391" t="n">
+        <v>327.02</v>
+      </c>
+      <c r="G391" t="n">
+        <v>386.64</v>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>265.8</v>
+      </c>
+      <c r="C392" t="n">
+        <v>326.62</v>
+      </c>
+      <c r="D392" t="n">
+        <v>330.44</v>
+      </c>
+      <c r="E392" t="n">
+        <v>323.4</v>
+      </c>
+      <c r="F392" t="n">
+        <v>327.69</v>
+      </c>
+      <c r="G392" t="n">
+        <v>389.45</v>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>255.03</v>
+      </c>
+      <c r="C393" t="n">
+        <v>328.7</v>
+      </c>
+      <c r="D393" t="n">
+        <v>332.82</v>
+      </c>
+      <c r="E393" t="n">
+        <v>325.47</v>
+      </c>
+      <c r="F393" t="n">
+        <v>328.47</v>
+      </c>
+      <c r="G393" t="n">
+        <v>391.48</v>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>248.6</v>
+      </c>
+      <c r="C394" t="n">
+        <v>328.7</v>
+      </c>
+      <c r="D394" t="n">
+        <v>332.82</v>
+      </c>
+      <c r="E394" t="n">
+        <v>323.72</v>
+      </c>
+      <c r="F394" t="n">
+        <v>326.43</v>
+      </c>
+      <c r="G394" t="n">
+        <v>391.48</v>
+      </c>
+      <c r="H394" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12064,7 +12244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B449"/>
+  <dimension ref="A1:B455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16557,6 +16737,66 @@
       </c>
       <c r="B449" t="n">
         <v>-0.88</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -16725,28 +16965,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9588932221924883</v>
+        <v>-0.961822325109813</v>
       </c>
       <c r="J2" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K2" t="n">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02159454132025529</v>
+        <v>0.02231256891965083</v>
       </c>
       <c r="M2" t="n">
-        <v>35.66235165502599</v>
+        <v>35.4042596494494</v>
       </c>
       <c r="N2" t="n">
-        <v>1875.793071407199</v>
+        <v>1854.081325876678</v>
       </c>
       <c r="O2" t="n">
-        <v>43.31042682088458</v>
+        <v>43.0590446465859</v>
       </c>
       <c r="P2" t="n">
-        <v>302.1276245708785</v>
+        <v>302.16510048304</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16803,28 +17043,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.963892428017042</v>
+        <v>-1.826371831112822</v>
       </c>
       <c r="J3" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K3" t="n">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1820675659345196</v>
+        <v>0.1609133375532433</v>
       </c>
       <c r="M3" t="n">
-        <v>19.8730961434155</v>
+        <v>20.06624721063554</v>
       </c>
       <c r="N3" t="n">
-        <v>799.076040503926</v>
+        <v>814.8844104470912</v>
       </c>
       <c r="O3" t="n">
-        <v>28.267933078029</v>
+        <v>28.54618031273346</v>
       </c>
       <c r="P3" t="n">
-        <v>337.3675454250783</v>
+        <v>335.6878929161934</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16881,28 +17121,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.97872053301242</v>
+        <v>-0.8977182022680323</v>
       </c>
       <c r="J4" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K4" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2866001942685659</v>
+        <v>0.2424002808441259</v>
       </c>
       <c r="M4" t="n">
-        <v>8.381710642604098</v>
+        <v>8.702060763083251</v>
       </c>
       <c r="N4" t="n">
-        <v>109.7601156735898</v>
+        <v>117.7947340770632</v>
       </c>
       <c r="O4" t="n">
-        <v>10.47664620351331</v>
+        <v>10.85332824883976</v>
       </c>
       <c r="P4" t="n">
-        <v>331.5262775546947</v>
+        <v>330.5365727886435</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16959,28 +17199,28 @@
         <v>0.0806</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7872821939903559</v>
+        <v>-0.7391878720325264</v>
       </c>
       <c r="J5" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K5" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2766012641192223</v>
+        <v>0.249393838096289</v>
       </c>
       <c r="M5" t="n">
-        <v>6.81255184642412</v>
+        <v>6.973704070202202</v>
       </c>
       <c r="N5" t="n">
-        <v>74.61997402340501</v>
+        <v>76.90865200015901</v>
       </c>
       <c r="O5" t="n">
-        <v>8.638285363624254</v>
+        <v>8.769757807383224</v>
       </c>
       <c r="P5" t="n">
-        <v>329.6748414862465</v>
+        <v>329.0872347177987</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17037,28 +17277,28 @@
         <v>0.059</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6658998373743691</v>
+        <v>-0.6221743301222974</v>
       </c>
       <c r="J6" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K6" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2261674342983083</v>
+        <v>0.2017818948255721</v>
       </c>
       <c r="M6" t="n">
-        <v>6.578625937854235</v>
+        <v>6.705825918858809</v>
       </c>
       <c r="N6" t="n">
-        <v>69.84018791560976</v>
+        <v>71.61478354203777</v>
       </c>
       <c r="O6" t="n">
-        <v>8.357044209265005</v>
+        <v>8.462551833935068</v>
       </c>
       <c r="P6" t="n">
-        <v>331.9185998527573</v>
+        <v>331.3844081745078</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17115,28 +17355,28 @@
         <v>0.1629</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3807994798925088</v>
+        <v>-0.3760065650197821</v>
       </c>
       <c r="J7" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="K7" t="n">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08951753131334528</v>
+        <v>0.08968222714636798</v>
       </c>
       <c r="M7" t="n">
-        <v>6.644461566827009</v>
+        <v>6.595003859579186</v>
       </c>
       <c r="N7" t="n">
-        <v>67.89328689476285</v>
+        <v>67.11454032384691</v>
       </c>
       <c r="O7" t="n">
-        <v>8.239738278292755</v>
+        <v>8.192346447987104</v>
       </c>
       <c r="P7" t="n">
-        <v>396.1931749007869</v>
+        <v>396.1344482259291</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17174,7 +17414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H388"/>
+  <dimension ref="A1:H394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33413,6 +33653,258 @@
         </is>
       </c>
     </row>
+    <row r="389">
+      <c r="A389" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>-45.78812132954592,170.74099641846374</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>-45.78876623968747,170.74094639376756</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>-45.78937772912835,170.74074165052374</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-45.789970326987806,170.74044533073373</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>-45.7905929544596,170.74029002080303</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>-45.79130031803886,170.7407732496229</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>-45.788067978158814,170.74074256879433</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>-45.788771960170784,170.7409750884104</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>-45.78937979102967,170.7407525776051</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-45.789971365464574,170.74045079141857</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>-45.79059230976581,170.74028614180673</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>-45.791309248153865,170.7408365390184</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>-45.78802733650603,170.74054919505184</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>-45.78875975482064,170.74091386493413</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>-45.789374027075674,170.740722031448</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-45.78996603146755,170.7404227433579</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-45.79058777610913,170.74025886370626</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-45.79131109821318,170.74084965076838</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>-45.787996867998125,170.7404042265209</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>-45.788759138387945,170.7409107728401</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>-45.789377494821316,170.74074040881</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-45.7899684860511,170.74043565042936</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>-45.790589169481365,170.74026724734216</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-45.791316096923715,170.74088507771285</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>-45.78796898798969,170.74027157491668</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>-45.78876426710537,170.74093649906453</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>-45.7893830713251,170.74076996159988</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-45.789973371612156,170.74046134046938</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-45.79059079161544,170.7402770073964</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-45.79131970808505,170.7409106708477</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-45.787952342749826,170.74019237815642</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-45.78876426710537,170.74093649906453</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-45.7893830713251,170.74076996159988</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-45.78996924130728,170.74043962183623</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-45.7905865491092,170.7402514811019</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-45.79131970808505,170.7409106708477</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0503/nzd0503.xlsx
+++ b/data/nzd0503/nzd0503.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H394"/>
+  <dimension ref="A1:H396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12213,10 +12213,10 @@
         <v>248.6</v>
       </c>
       <c r="C394" t="n">
-        <v>328.7</v>
+        <v>314.46</v>
       </c>
       <c r="D394" t="n">
-        <v>332.82</v>
+        <v>328.56</v>
       </c>
       <c r="E394" t="n">
         <v>323.72</v>
@@ -12228,6 +12228,66 @@
         <v>391.48</v>
       </c>
       <c r="H394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>231.73</v>
+      </c>
+      <c r="C395" t="n">
+        <v>297.82</v>
+      </c>
+      <c r="D395" t="n">
+        <v>323.02</v>
+      </c>
+      <c r="E395" t="n">
+        <v>320.86</v>
+      </c>
+      <c r="F395" t="n">
+        <v>325.54</v>
+      </c>
+      <c r="G395" t="n">
+        <v>392.82</v>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>214.14</v>
+      </c>
+      <c r="C396" t="n">
+        <v>281.98</v>
+      </c>
+      <c r="D396" t="n">
+        <v>320.82</v>
+      </c>
+      <c r="E396" t="n">
+        <v>319.52</v>
+      </c>
+      <c r="F396" t="n">
+        <v>323.44</v>
+      </c>
+      <c r="G396" t="n">
+        <v>398.69</v>
+      </c>
+      <c r="H396" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12244,7 +12304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B455"/>
+  <dimension ref="A1:B457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16797,6 +16857,26 @@
       </c>
       <c r="B455" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -16965,28 +17045,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.961822325109813</v>
+        <v>-1.01956863610354</v>
       </c>
       <c r="J2" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K2" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02231256891965083</v>
+        <v>0.02505524985601015</v>
       </c>
       <c r="M2" t="n">
-        <v>35.4042596494494</v>
+        <v>35.551698322394</v>
       </c>
       <c r="N2" t="n">
-        <v>1854.081325876678</v>
+        <v>1859.519776917091</v>
       </c>
       <c r="O2" t="n">
-        <v>43.0590446465859</v>
+        <v>43.12214949323713</v>
       </c>
       <c r="P2" t="n">
-        <v>302.16510048304</v>
+        <v>302.8857649046988</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17043,28 +17123,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.826371831112822</v>
+        <v>-1.830462989728261</v>
       </c>
       <c r="J3" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K3" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1609133375532433</v>
+        <v>0.1632617110217155</v>
       </c>
       <c r="M3" t="n">
-        <v>20.06624721063554</v>
+        <v>19.9730202441859</v>
       </c>
       <c r="N3" t="n">
-        <v>814.8844104470912</v>
+        <v>808.6041477390844</v>
       </c>
       <c r="O3" t="n">
-        <v>28.54618031273346</v>
+        <v>28.43596574303543</v>
       </c>
       <c r="P3" t="n">
-        <v>335.6878929161934</v>
+        <v>335.7378897575816</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17121,28 +17201,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8977182022680323</v>
+        <v>-0.8838373534703617</v>
       </c>
       <c r="J4" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K4" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2424002808441259</v>
+        <v>0.2375204832251133</v>
       </c>
       <c r="M4" t="n">
-        <v>8.702060763083251</v>
+        <v>8.736302112889698</v>
       </c>
       <c r="N4" t="n">
-        <v>117.7947340770632</v>
+        <v>117.8766670667955</v>
       </c>
       <c r="O4" t="n">
-        <v>10.85332824883976</v>
+        <v>10.85710214867648</v>
       </c>
       <c r="P4" t="n">
-        <v>330.5365727886435</v>
+        <v>330.3662561217057</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17199,28 +17279,28 @@
         <v>0.0806</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7391878720325264</v>
+        <v>-0.727823780636947</v>
       </c>
       <c r="J5" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K5" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L5" t="n">
-        <v>0.249393838096289</v>
+        <v>0.244086145024849</v>
       </c>
       <c r="M5" t="n">
-        <v>6.973704070202202</v>
+        <v>7.002258799771615</v>
       </c>
       <c r="N5" t="n">
-        <v>76.90865200015901</v>
+        <v>77.11479179569862</v>
       </c>
       <c r="O5" t="n">
-        <v>8.769757807383224</v>
+        <v>8.781502821026628</v>
       </c>
       <c r="P5" t="n">
-        <v>329.0872347177987</v>
+        <v>328.9478496428978</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17277,28 +17357,28 @@
         <v>0.059</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6221743301222974</v>
+        <v>-0.6119920035931048</v>
       </c>
       <c r="J6" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K6" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2017818948255721</v>
+        <v>0.1970624109503455</v>
       </c>
       <c r="M6" t="n">
-        <v>6.705825918858809</v>
+        <v>6.724980009753123</v>
       </c>
       <c r="N6" t="n">
-        <v>71.61478354203777</v>
+        <v>71.73407844401595</v>
       </c>
       <c r="O6" t="n">
-        <v>8.462551833935068</v>
+        <v>8.46959730117176</v>
       </c>
       <c r="P6" t="n">
-        <v>331.3844081745078</v>
+        <v>331.2595204887123</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -17355,28 +17435,28 @@
         <v>0.1629</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3760065650197821</v>
+        <v>-0.3659029920737821</v>
       </c>
       <c r="J7" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K7" t="n">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08968222714636798</v>
+        <v>0.08553130035289847</v>
       </c>
       <c r="M7" t="n">
-        <v>6.595003859579186</v>
+        <v>6.608619871175023</v>
       </c>
       <c r="N7" t="n">
-        <v>67.11454032384691</v>
+        <v>67.2870862481935</v>
       </c>
       <c r="O7" t="n">
-        <v>8.192346447987104</v>
+        <v>8.202870610231122</v>
       </c>
       <c r="P7" t="n">
-        <v>396.1344482259291</v>
+        <v>396.0105036778326</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -17414,7 +17494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H394"/>
+  <dimension ref="A1:H396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33876,12 +33956,12 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>-45.78876426710537,170.74093649906453</t>
+          <t>-45.78872915500259,170.74076037347277</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>-45.7893830713251,170.74076996159988</t>
+          <t>-45.78937308984661,170.7407170645938</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -33900,6 +33980,90 @@
         </is>
       </c>
       <c r="H394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>-45.78790867138898,170.73998459466577</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>-45.78868812479045,170.74055456408504</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>-45.78936010920229,170.7406482736812</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-45.78996249120026,170.7404041273915</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-45.790584698210104,170.74024034463153</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-45.791322091804204,170.74092756484015</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>-45.78786313576798,170.73976794347854</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>-45.78864906684501,170.7403586496724</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>-45.78935495442245,170.74062095599953</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-45.78995932855897,170.74038749713029</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-45.79058033091585,170.74021406756972</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-45.79133253388804,170.74100157063106</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
